--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,7 +666,7 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="79378-6"/&gt;
-    &lt;display value="Cause of death"/&gt;
+    &lt;display value="Causes du décès"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,7 +666,7 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="79378-6"/&gt;
-    &lt;display value="Causes du décès"/&gt;
+    &lt;display value="Cause of death"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-cause-mortalite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
